--- a/update/historicos/tpm_uyu.xlsx
+++ b/update/historicos/tpm_uyu.xlsx
@@ -199,7 +199,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="2" max="2" width="35.1" customWidth="1"/>
